--- a/260905.xlsx
+++ b/260905.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ADDEB03-CAC3-48BF-8BB1-95770E1FE974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F31D471-7A26-4042-BC1F-1E5D14FBA056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10570" yWindow="4110" windowWidth="15030" windowHeight="11170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4490" yWindow="2140" windowWidth="15030" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,103 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>每周采访-160731-Generalbundesanwalt</t>
-  </si>
-  <si>
-    <t>每周采访-160807-Bundesweh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每周采访-160828-Frod</t>
-  </si>
-  <si>
-    <t>每周采访-160904-Kolner</t>
-  </si>
-  <si>
-    <t>Und hier muss jeder Staatsanwalt frühzeitig wissen – nicht nur der Staatsanwalt, der sich in einer Spezialabteilung befindet –, muss sich jeder Staatsanwalt frühzeitig bewusst werden: Gibt es hier Erkenntnisse, die darauf hindeuten, dass es sich um einen rechtsextremistischen Hintergrund handelt?
-Und insoweit haben wir versucht, jeden Staatsanwalt und im Übrigen auch versucht, jeden Vollzugsbeamten – denn man muss auch im Strafvollzug erkennen: Jemand, der wegen eines Diebstahls, eines Ladendiebstahls sitzt, auch der kann einen rechtsextremistischen Hintergrund haben – frühzeitig diese Strukturen zu erkennen, um sie dann den zuständigen Behörden zu melden, damit sich daraus nichts verfestigt.
-Geuther: Es gab im vergangenen Jahr fast 1.500 politisch rechts motivierte Gewalttaten und darunter eine bisher nie gehabte Zahl von Angriffen auf Flüchtlingsunterkünfte.
-Wie gehen Sie als Generalbundesanwalt damit um?
-Frank: Für die Beobachtung von rechtsextremistischen Straftaten gibt es im Bundesamt für Verfassungsschutz das gemeinsame Extremismus- und Terrorismusabwehrzentrum rechts, in dem auch wir – die Bundesanwaltschaft – vertreten sind.
-In diesem Zentrum, das eine Plattform darstellt, in dem Polizeibehörden, Dienste, Nachrichtendienste, aber auch die Staatsanwaltschaft vertreten ist, werden solche Vorfälle gemeinsam bewertet.
-Wir, die Bundesanwaltschaft, schauen uns diese schwerwiegenden Straftaten, wenn sie ein bestimmtes Ausmaß erreicht haben, immer wieder an, um dort auch herauszufinden, ob sich Strukturen bilden.
-Das ist eine der Konsequenzen auch der Ergebnisse aus der Aufarbeitung NSU, dass wir verschiedene Strukturverfahren angelegt haben, um frühzeitig herauszufinden: Welche Entwicklungen spielen sich in bestimmten Bereichen ab?
-Wir haben – gerade, was die Anschläge auf die Flüchtlingsheime im letzten Jahr anbelangt – Strukturen, Verfahren geführt, um festzustellen: Gibt es Vernetzungen?
-Sind das nur Taten von Einzelpersonen oder von lokalen kleineren Gruppierungen?
-Oder hat sich da eine größere Vernetzungsstruktur gebildet?
-Findet da vielleicht eine Steuerung aus einem etwas größeren Ganzen statt?
-Wir haben auch im Blick, zusammen mit den Polizei- und den Verfassungsschutzbehörden: rechtsextremistische Musikgruppen.
-Wir haben im Blick besonders: rechtsextremistische Gefährder.
-Wir stehen insoweit in einem engen Kontakt und Austausch mit dem Bundeskriminalamt.
-Wir kriegen in regelmäßigen Abständen alle Gefährder aus dem rechtsextremistischen Bereich gemeldet, die wir dann wiederum mit unseren Erkenntnissen versuchen abzuklären.
-Nur, wenn man versucht, das Phänomen Bereich Rechtsextremismus ganzheitlich zu betrachten und unter allen möglichen Aspekten und Blickwinkeln auch zu durchleuchten, dann lässt sich frühzeitig verhindern, dass sich wieder eine neue Struktur NSU bildet.
-Das ist für uns sehr wichtig.
-Geuther: Jetzt haben wir über Rechtsextremismus gesprochen, vorher über den Islamismus, über eine Amok-Tat.
-Gleichzeitig waren laut Verfassungsschutzbericht auch Linksextremisten im vergangenen Jahr deutlich gewalttätiger als zuvor.
-Und man könnte auch weitergehen.
-Die Verrohung steigt offenbar insgesamt.
-Nicht nur in der Sprache im Internet, auch im öffentlichen Dienst, im Arbeitsamt oder in der Ausländerbehörde werden Mitarbeiter öfter angegriffen.
-Was kann Recht da überhaupt leisten?
-Frank: Es ist seit längerer Zeit zu erkennen, dass die Gewaltbereitschaft in Deutschland zugenommen hat.
-Und so, wie Sie es beschrieben haben, es beginnt zunächst einmal mit einer Verrohung der Sprache.
-Und es führt dann zu einer Verrohung auch in der körperlichen Auseinandersetzung.
-Seit Jahren steigt der Anteil von Gewaltstraftaten.
-Und auch, wenn man sich die Entwicklung innerhalb der Gewaltstraftaten anschaut, so findet man immer wieder einen Anstieg auch der Vehemenz von Gewalt.
-Recht – und das ist das Entscheidende und Wichtige von Recht – Recht muss immer durchgesetzt werden.
-Recht muss insoweit standhaft bleiben, denn sonst verliert das Recht seine Achtung.
-Wir haben in Deutschland Werte letztendlich immer durch Rechtsnormen versucht auch abzusichern und Werteentfaltung durch das Schaffen von Recht einen Rahmen zu geben.
-Und nur, wenn wir diesen Rechtsrahmen auch konsequent verteidigen – und dazu gehört eine konsequente Strafverfolgung – nur, wenn wir diesen Rechtsrahmen verteidigen, dann haben wir eine Chance, dass das Recht und damit auch die Werte erhalten bleiben.
-Geuther: Herr Generalbundesanwalt, vielen Dank für das Gespräch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>es habe eigentlich gar keine persönlichen Beziehungen zu dieser Abgeordneten gegeben.
-Schlagen sich da ein paar Genossen jetzt im Nachhinein in die Büsche?
-Oder wirft diese Affäre ein Schlaglicht auf eine für die Politik vielleicht typische Verkümmerung von menschlichen Beziehungen?
-Scholz: Letzteres ganz bestimmt nicht.
-Wie es dazu gekommen ist, dass das niemand bemerkt hat, auch die ja immer sehr kritische Öffentlichkeit und Presse nicht.
-Das kann ich mir auch nicht so richtig erklären.
-Auf alle Fälle, wenn alles zu Ende ist, wird es sicherlich ein gutes Buch über das Thema geben und dann werden wir mehr lernen.
-Detjen: Sie haben vor ein paar Wochen, Herr Scholz, ein Papier geschrieben, das trug die Überschrift: Die Partei der schlechten Laune.
-Das bezog sich nicht auf die SPD, richtig?
-Scholz: Klar, das bezog sich auf die AfD.  Dafür sorgen, dass es eine gute Zukunft gibt Detjen: Warum ist die für Sie die  Partei der schlechten Laune ?
-Scholz: Weil es ja keine konkreten Vorstellungen gibt darüber, wie es weitergehen soll mit unserem Land, sondern vor allem der Eindruck erweckt wird, alles läuft schief und es geht in die falsche Richtung.
-Ich glaube, dass es immer wichtig ist, dass man Vorstellungen dafür hat, wie man mit demokratischer Politik unser Land besser machen kann und dass man sich auch auf ganz, ganz, ganz konkrete Fragen beziehen muss.
-Was machen wir mit unseren öffentlichen Haushalten?
-Wie statten wir die Bundeswehr und unsere Polizei gut aus?
-Was machen wir, um die Bildung zu verbessern an den Schulen?
-Wie setzen wir Forschung und Universitäten auf die richtige Spur?
-Also immer ganz konkrete Politik, bei der es darum geht: Wie können wir dafür sorgen, dass es eine gute Zukunft gibt.
-Und über sowas muss man diskutieren.
-Und ich glaube, dass das auch der richtige Umgang ist in der Sache.
-Detjen: Dann werfen wir am Ende des Gesprächs nochmal den Blick auf das konkrete Thema, das uns alle, das das Land im vergangenen Jahr am meisten beschäftigt hat.
-Vor einem Jahr um diese Zeit schwante den meisten, dass mit der Flüchtlingsbewegung eine riesige Aufgabe, eine Generationenaufgabe auf Bund, Länder, Kommunen zukommen.
-Wenn Sie jetzt Hamburg anschauen, was sich in diesem Jahr getan hat, ist das für Sie ein Anlass, gut gelaunt auf die Entwicklung zu schauen oder eher schlecht gelaunt?
-Scholz: Was letztes Jahr stattfand, war eine unglaubliche Herausforderung.
-Und – das, glaube ich, muss man auch ganz offen sagen – in Deutschland war nicht überall klar, wer wann wo ist und wer wohin kommen soll und wer wo aufgenommen wird.
-Mittlerweile sind viele Institutionen, insbesondere auch das Bundesamt für Migration und Flüchtlinge, massiv ausgebaut worden.
-Dieser Ausbauprozess ist noch nicht beendet, das muss nun bald erfolgen.
-Und wir müssen mit den gesetzlichen Änderungen, die wir ergriffen haben, mit all den Maßnahmen, die wir getroffen haben, vorbereitet sein auf solche Entwicklungen.
-Das muss das Ergebnis des letzten Jahres sein.
-Denn wir können ja nicht sicher sein, dass nicht irgendwann mal wieder eine große Zahl von Flüchtlingen kommt.
-Jetzt sieht es ein wenig danach aus, dass es weniger werden und wir uns jetzt auf die Aufgabe konzentrieren können, diejenigen, die länger bleiben werden, zu integrieren.
-Detjen: Nochmal der Blick konkret auf Hamburg.
-Was haben Sie geschafft in diesem Jahr?
-Scholz: Wir haben Tausende von Unterkunftsplätzen geschaffen, was nicht ganz einfach ist in einer Stadt, die sehr bebaut ist und relativ mehr Flüchtlinge aufnimmt als andere, weil bei der Verteilung der Flüchtlinge in Deutschland Bevölkerungszahl und Wirtschaftskraft eine Rolle spielen und nicht die Frage 'Wieviel Platz hat man so?
-'.
-Das haben wir aber gemeistert und haben uns auch über viele Standorte verständigt, haben mit vielen Bürgerinnen und Bürgern gesprochenen, verhandelt, haben unglaublich viel Unterstützung bekommen von denjenigen, die in den Flüchtlingsunterkünften helfen.
-Und wir haben sofort dafür gesorgt, dass mehr Angebote gemacht werden bei Krippen und Kitas, bei den Schulen, haben zusätzliche Lehrerinnen und Lehrer eingestellt, damit es ohne Beeinträchtigung des bisherigen Betriebs zu einer schnellen Integration der jungen Leute kommt.
-Wir haben uns sofort darauf konzentriert, diejenigen, die in dem Alter sind, in dem man zur Berufsschule geht, dort auszubilden, auch mit einer Berufsorientierung zu versehen.
-Und wir haben Angebote entwickelt, die für diejenigen, die erwachsen sind, eine Arbeitsmarktintegration in den Blick nehmen.
-Detjen: Und vieles ist noch zu tun.
-Würden Sie Ihren Bürgerinnen und Bürgern in Hamburg sagen:  Wir schaffen das ?
-Scholz: Wer realistisch ist, kann immer nur sagen: Wir können das schaffen.
-Aber die Bürgerinnen und Bürger haben einen großen Beitrag dazu geleistet, dass zusammen mit einer sehr engagierten Verwaltung wir ganz schön weit gekommen sind und uns jetzt an die nächsten Aufgaben machen.
-Detjen: Herr Bürgermeister, vielen Dank.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>dass der Stärkste sich davor drückt, zum Gemeinwohl beizutragen.
 Geers: Das heißt aber auch, aus Ihrer Sicht wackelt dann zum Beispiel das Thema Haushaltsausgleich – dann wackelt die schwarze Null nicht unbedingt?
@@ -138,64 +42,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>in dieses Qualifizierungsprogramm bringen, wo sie eben soweit fit gemacht werden, dass sie dann im Arbeitsmarkt in eine reguläre Ausbildung einsteigen können.
-Und das hat sich bewährt und wir sind froh, dass wir eben diese Plätze auch bereitstellen können.
-Denn wichtig ist, dass die Menschen, die es wollen, tatsächlich auch die Voraussetzungen schaffen, um dann im Arbeitsmarkt erfolgreich sein zu können.
-Hahne: Arbeiten die eigentlich nur in der Produktion oder auch in der Verwaltung?
-Mattes: Nein, die sind in der Produktion, und da können wir auch genau sehr schön im Prinzip abbilden, was die Leute können und was die Leute wollen, und das passt hervorragend zusammen.
- Protektionismus ist in einer immer vernetzteren Welt genau das Falsche Hahne: Sie sind nicht nur als Manager in einem deutsch-amerikanischen Konzern ein USA-Kenner, Sie waren schon als Jugendlicher das erste Mal in den USA bei einer Gastfamilie.
-Aktuell läuft ja dort der Präsidentschaftswahlkampf auf Hochtouren.
-Beide Kandidaten schlagen protektionistische Töne an.
-Sorgt Sie das einerseits als USA-Liebhaber, andererseits aber auch als Manager?
-Die USA sind ja immerhin auch der wichtigste Exportmarkt für Deutschland.
-Mattes: Grundsätzlich, ungeachtet jetzt des Präsidentschaftswahlkampfs, ist Protektionismus in einer immer vernetzteren Welt genau das Falsche.
-Freier und fairer Handel, offene Grenzen – aber wie ich sagte, fair auch was Währungsgestaltung angeht –, das ist etwas, was wir befürworten, was ich befürworte, was Ford befürwortet und was auch sicherlich für die USA schon immer etwas war.
-Die USA war immer offen, offen in der Entwicklung neuer Ideen und diese dann auch in die Welt hinauszutragen und nicht nur für sich selber zu sorgen.
-Von daher gesehen bin ich überzeugt, dass es das richtige Mittel ist, weiterhin freien und fairen Handel und wenig Protektionismus zu fordern und zu fördern.
-Wir werden sehen, welcher der Kandidaten letztlich Präsidentin oder Präsident wird.
-Und ich bin überzeugt, dass der Grundsatz von freiem und fairen Handel auch den nächsten Präsidenten oder die nächste Präsidentin schnell überzeugen wird.
-Hahne: Haben Sie da bei Clinton oder Trump größere Hoffnung, bei dem ein oder anderen Kandidaten?
-Mattes: Ich sehe zumindest in den Ankündigungen, dass Frau Clinton eher für einen offenen Handel ist, sicherlich sehr dezidiert und unterschiedlich, was die derzeit diskutierten Freihandelsabkommen angeht – das transpazifische eher kritisch, das europäisch-amerikanische, glaube ich, eher offen.
-Natürlich weist sie auf einige Punkte hin, wie Arbeitnehmerrecht und Ähnliches, aber das ist klar.
-Das ist in den Verhandlungen jetzt auch noch zu Ende zu verhandeln, aber vom Grundsatz her, glaube ich, ist da eine Offenheit da.
-Starke Wettbewerbsposition für mehr Innovation und sichere Arbeitsplätze Hahne: Hillary Clinton wäre Ihnen also die liebere US-Präsidentin?
-Mattes: Das will ich jetzt damit nicht gesagt haben.
-Ich glaube auch, dass ein anderer Präsident, nämlich Donald Trump als Wirtschafskenner, sehr schnell erkennt, dass Protektionismus keine Dauerlösung ist, sondern letztlich Weltoffenheit, wenn es darum geht, Innovationen, Investitionen und auch Handel zu fördern, das richtige Mittel ist.
-Hahne: Es klang ja schon an, Sie sind auch Befürworter des Freihandelsabkommens TTIP. Mittlerweile ist ja nicht mehr so sicher, ob das bis November abschließend verhandelt wird und ob es danach eine Chance hat, das wird dann eben die Zukunft zeigen.
-Würden Sie im Zweifelsfall – anders als früher – jetzt auch für einen Teilbeschluss von einzelnen Paketen plädieren?
-Mattes: Das hat zwei Aspekte.
-Auf der einen Seite, wenn man sich heute dazu durchringt zu sagen: Okay, wir machen einen Teilabschluss – dann hat man vielleicht einen Teilsieg errungen, indem wir einen Teil von Reglungen tatsächlich dann harmonisieren und offen gestalten, aber das Andere ist dann eben nicht geregelt.
-Und deswegen bin ich nach wie vor dafür, keine Ausschlüsse zu machen und ein so umfassend wie mögliches Abkommen zu gestalten und einen Rahmenentwurf bis zum Jahresende zu setzen, der ja dann erstmal in die parlamentarische Beratung auch geht und sowohl in den USA als auch in den europäischen Ländern zu diskutieren ist.
-Möglichst umfassend ist wichtiger als Zeit.
-Zeit ist aber auch drängend, denn wir sind ja nicht alleine im Welthandel, Europa und Amerika.
-Und je mehr Zeit ins Land geht, desto weniger stärken wir die Wettbewerbsposition von Europa und Amerika im Welthandel und das sollten wir uns immer vor Augen führen: Eine starke Wettbewerbsposition hat zum Beispiel auch zur Folge, dass die in diesen Ländern ansässigen Industrien eine bessere Möglichkeit haben, Arbeitsplätze zu sichern, Innovationen zu fördern und letztlich auch Investitionen zu treiben, die weitere Arbeitsplätze schaffen können.
- Am Anfang hätte man transparenter informieren sollen Hahne: Stichwort  parlamentarische Beratung , wie zufrieden stellt Sie denn – als Bürger Bernhard Mattes und nicht als Ford-Chef Bernhard Mattes – der Ablauf der Verhandlungen, der ja insbesondere am Anfang doch recht intransparent war?
-Mattes: Ja, ich habe das persönlich auch genauso gesehen, wie Sie es eben fragen.
-Am Anfang hätte man transparenter informieren sollen.
-Das Mandat, das der EU-Kommission gegeben wurde, ist sehr klar, es wurde von allen 27 Mitgliedsstaaten ratifiziert.
-Das hätte man ohne Weiteres zu Beginn der Verhandlungen und nicht erst zwei Jahre später veröffentlichen können.
-Denn darin können heute alle Bürger lesen – jetzt ist es ja schon lange transparent und im Internet verfügbar –, was sind denn eigentlich die Grundlinien und Richtwerte und Felder der Verhandlungen.
-Da ist alles sehr transparent beschrieben.
-Da ist auch klar beschrieben, in welche Richtung zu verhandeln ist, was das Mandat ist und was es nicht ist.
-Das hätte man früher machen sollen.
-Hahne: Und jetzt nochmal Frage an den Manager: Besonders kritisch diskutiert werden ja die Schiedsgerichte nach wie vor – die politischen Systeme in den USA und Europa bieten Unternehmen ja ziemlich viel Rechtssicherheit.
-Halten Sie Schiedsgerichte trotzdem für ein geeignetes Instrument zum Investorenschutz?
-Mattes: Auf jeden Fall.
-Und ich halte das auch innerhalb von TTIP für das richtige Instrument.
-Weil TTIP kann auch eine Art Blaupause für weitere Freihandelsabkommen sein oder auch ein Abkommen eines Wirtschaftsraumes, der sich weiter öffnen kann, auch weitere Mitglieder noch aufnehmen kann.
-Und um genau diese Möglichkeit aufrecht zu erhalten, sollte man über den Investorenschutz und die Schiedsgerichte auch hier eine Klausel finden.
-Wir haben es ja auch in CETA, in dem Abkommen zwischen der EU und Kanada drin – auch zwei Systeme, die absolut von der Rechtssicherheit in Ordnung sind.
-Es gibt natürlich schon ein Gefälle auch innerhalb der EU, das darf man nicht verkennen.
-Trotzdem, die Bundesrepublik Deutschland hat in 130 Fällen in Freihandelsabkommen Schiedsgerichtsklauseln und Investorenschutzabkommen verankert.
-Um einfach eines sicherzustellen, dass Firmen sowohl im Inland als auch im Ausland, wenn es um willkürliche Veränderungen und Diskriminierung geht, hier vorgehen können.
-Es gilt auch für kleinere Unternehmen, kleinere und mittlere, die mittlerweile ja auch global unterwegs sind, die im Zweifelsfall gar nicht die Möglichkeit haben, weil sie gar nicht die Rechtsabteilungen in ihren Unternehmen haben, ihre Rechte einzufordern.
-Es geht nicht darum, dass man gegen bestehendes Gesetz und Recht klagen kann, dafür ist die normale Gerichtsbarkeit zuständig.
-Das ist auch ein wichtiger Unterschied, der zu machen ist.
-Hahne: Herr Mattes, vielen Dank für das Gespräch.
-Mattes: Bitteschön.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ist die Anzahl der Belegschaft nicht zurückgegangen.
 Es hat sich aber ein Wandel in den Arbeitsplätzen ergeben, wie ich vorhin schon.
 Wir haben ein hohes Maß an Training aufgewandt in den letzten Jahren.
@@ -205,165 +51,6 @@
 Ford hat ein Praktikantenprogramm ?
 Mattes: in mehrerlei Hinsicht.
 Erstens einmal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sich an der Herausforderung beteiligt – und das tut sie auch.
-Küpper: Wie erklären Sie sich dann, dass es doch ab und zu immer mal wieder Diskussionen gibt, auch gerade jetzt in der aktuellen Situation?
-Reker: Na ja, man muss eben seine Haltung, gerade in der aktuellen Situation, man muss seine Haltung immer wieder überprüfen und immer wieder an ihren Taten messen.
-"""""""""""""""" Ich finde das sehr mutig von der Kanzlerin"""""""""""""""" Küpper: Organisation, Finanzierung, auch die Zusammenarbeit, über die wir gerade gesprochen haben – zumindest die mit den muslimischen Verbänden –, das ist ja ein Teil, ein anderer Punkt ist die Haltung in dieser Flüchtlingsfrage.
-Die Bundeskanzlerin hat das ja sehr deutlich gemacht mit drei Worten, die immer wieder zitiert werden, die auch in dieser Woche ja viel diskutiert wurden, weil es ja jetzt ein Jahr sozusagen her ist, dass sie gesagt hat, """""""""""""""" Wir schaffen das! """""""""""""""" Warum stimmt dieser Satz noch?
-Reker: Ich habe diesen Satz damals und auch heute noch als Aufforderung verstanden, zusammen – jeder nach seinen Kräften – der Welt ein freundliches Gesicht zu zeigen.
-Und ich finde das gut, dass Deutschland das getan hat.
-Wenn man sich nur mal vorstellt, was denn passiert wäre, wenn die Grenzen da nicht geöffnet worden wären, wenn sie verschlossen geblieben wären, abgesehen davon, dass es gegen unser Grundrecht auf Asyl verstoßen hätte und gegen die Genfer Flüchtlingsgesetze.
-Aber dann hätte es auf der Balkanroute einen Stau gegeben von, ich weiß nicht, mehreren hunderttausend Menschen, die dann da verrottet wären?
-Oder was wäre passiert?
-Also, ich finde das sehr mutig von der Kanzlerin und ich finde es sehr human, dass sie hier dafür gesorgt hat, dass Schlimmeres, und zwar menschliche Katastrophen verhindert worden sind.
-"""""""""""""""" In Deutschland kann es keine Obergrenze für Asyl geben"""""""""""""""" Küpper: War es alternativlos?
-Reker: Nein, es war nicht alternativlos.
-Es war eben human und überlegt, diese Entscheidung so zu treffen und sie entsprach unserem Grundgesetz, nämlich die Diskussion über die Obergrenzen, die ist einfach nicht wahrhaftig.
-In Deutschland kann es keine Obergrenze geben, weil jeder, der in dieses Land kommt, einen Antrag auf Asyl erst einmal stellen kann.
-Und da kann man nicht beim Dreihunderttausendersten sagen: 'Du jetzt nicht mehr'.
-Küpper: Die Flüchtlingspolitik und auch gerade, wie sie in der Bevölkerung ankommt, das muss man ja auch gerade als jemand in öffentlichen Ämtern, gerade als jemand, der dieses Land mit führt, auch erklären.
-"""""""""""""""" Wir schaffen das! """""""""""""""" – nimmt dieser Satz die Bevölkerung genug mit?
-Reker: Offensichtlich reicht es als Erklärung nicht.
-Es muss immer damit verbunden werden, wie wir das schaffen – ich glaube, dann wird es leichter.
-Und dieses """""""""""""""" wie wir das schaffen"""""""""""""""" , daran muss sich natürlich der Bund und das Land beteiligen.
-Da kommen wir wieder zu den ...
-Küpper: Liegt dieses """""""""""""""" wie"""""""""""""""" noch zu sehr bei den Kommunen?
-Reker: Das """""""""""""""" wir"""""""""""""""" liegt noch zu sehr bei den Kommunen und auch die Erklärung, dass sich eben unsere Gesellschaft verändern wird im Rahmen der Globalisierung dieser Welt, ob wir das wollen oder nicht.
-So frühzeitig wie möglich, diese Veränderung mitzugestalten, darum geht es hier.
-Und mitzugestalten heißt eben auch, Integrationsmaßnahmen sehr frühzeitig beginnen zu können.
-Dazu gehören die Integrationskurse, die ja Bundessache sind.
-Aber bitte nicht hintereinander, erst einen Sprachkurs und dann Integrationskurs, sondern parallel, dass da eine schnellere Integration möglich ist.
-Rechtzeitige Beschulung, Kindergartenplätze.
-Und es ist natürlich klar, dass angespannte Haushalte dann unter diesen Kosten leiden und dass die Bürgerinnen und Bürger wenig Verständnis dafür haben werden, wenn sie an der einen Stelle einsparen sollen, damit dann – normalerweise vom Bund zu übernehmende – Integrationsmaßnahmen durchgeführt werden.
-Also, das kann man dadurch lösen, dass das Geld kommt.
-Küpper: Stellen Sie fest, in der Bevölkerung, bei Ihren Gesprächen – Sie machen ja auch viele Gespräche mit Bürgern –, dass den Leuten klar ist, dass das eine jahre-, wenn ich vielleicht sogar jahrzehntelange Aufgabe jetzt wird?
-Reker: Es wird ihnen allmählich klar.
-Also, ich glaube, dass der Prozess eingesetzt hat, dass man jetzt darüber nachdenkt, dass diese Menschen eben nicht nur kurzzeitig hierhinkommen und wieder gehen, sondern hierbleiben und was das auch für Nachbarschaften bedeutet, was das für Schulen bedeutet.
-Und ich muss nach wie vor sagen, die Kölner gehen damit wunderbar um.
-"""""""""""""""" Die Reflektion des Täters ist für mich nach wie vor schleierhaft"""""""""""""""" Küpper: Auch Sie wurden ja mit diesem schweren Attentat, das auf Sie verübt wurde, ja ein Stück weit für Merkels Flüchtlingspolitik verantwortlich gemacht – so war es zumindest, so hat der Attentäter das damals ein Stück weit begründet.
-Haben Sie für sich diese Verbindung auch schon einmal herstellt, dieses """""""""""""""" Wir schaffen das"""""""""""""""" und dieses Attentat dann letztendlich?
-Reker: Also, in den Vorstellungen des Täters ist es so gewesen.
-Aber ich habe ja vor diesem Attentat keine flammenden Reden zur Flüchtlingsunterbringung gehalten, sondern ich habe meine Aufgabe erledigt.
-Küpper: Als Sozialdezernentin.
-Reker: Als Sozialdezernentin – nicht mehr und nicht weniger.
-Und ich haben eben immer offen und ehrlich darauf hingewiesen, dass ich vorschlage, das zu akzeptieren und mit dieser Situation zu leben und sich dem positiv zu nähern.
-Aber die Reflektion des Täters ist sowieso für mich völlig schleierhaft.
-Küpper: Wie präsent ist dieses Attentat bei Ihnen noch im Alltag?
-Reker: Es ist jeden Tag präsent.
-Ich leide da nicht drunter, ich habe auch keine Zeit, da lange drüber nachzudenken, aber ich werde eben offen auch darauf angesprochen und mittlerweile kann ich damit wirklich ganz gut umgehen.
-"""""""""""""""" Wir müssen eine angemessene, ruhige, argumentative politische Kultur pflegen"""""""""""""""" Küpper: Bei Ihrem ersten öffentlichen Auftritt nach diesem Attentat und auch nach der Wahl, bei der Verleihung des Heinrich-Böll-Preises an die Schriftstellerin Herta Müller, da hat diese gesagt: """""""""""""""" Wenn Worte, wie 'Volksverräter' und 'Lügenpresse' langegenug spazieren gehen, geht auch mal ein Messer spazieren."""""""""""""""" Wir erleben es ja in Deutschland immer noch tagtäglich, was für eine teilweise rohe und aufgeheizte Debatte wir führen, sei es in den sogenannten """""""""""""""" Sozialen Netzwerken"""""""""""""""" , aber auch anderswo.
-Wird genug getan, diesem Satz, den Herta Müller da ja gesagt hat, den umzusetzen, dem Einhalt zu gebieten, dieser Verrohung teilweise der Diskussion?
-Reker: Der Satz von Herta Müller, dass erst Parolen spazieren gehen und dann Messer – ich sage es mal jetzt sinngemäß –, den zitiere ich oft, weil ich glaube, dass der genau stimmt.
-Und diese politische Kultur der Auseinandersetzung, die führt – davon bin ich zutiefst überzeugt – dazu, dass dann auch es zu solchen Tätlichkeiten kommt.
-Weil man muss sich ja mal vorstellen, es gehört ja eine gewisse Überwindung dazu, jemandem ein Messer irgendwie in den Körper zu stechen.
-Das kommt nicht von selbst und da muss eben ein Hasspotenzial aufgebaut sein, was auch nicht von selbst entsteht.
-Und wenn das immer wieder unterstützt wird durch Parolen, durch Menschen, die die Situation befeuern, um ihre eigenen Interessen zu schüren, um ihr Süppchen kochen zu wollen – ohne eine Alternative allerdings zu haben –, dann wird das gefährlich für uns alle.
-Und deswegen trete ich immer dafür ein, dass wir auch eine angemessene, ruhige, argumentative politische Kultur pflegen.
-Küpper: Was kann man da tun?
-Sie sind Juristin.
-Reichen da Gesetze oder ist das eher eine gesellschaftliche Sache?
-Reker: Es ist eine gesellschaftliche Sache, es ist nicht alles justiziabel, was da passiert, das sehen wir ja an Demonstrationen und an Gewalt in den Demonstrationen.
-Ich glaube, dass man da ganz früh ansetzen muss.
-Und ich glaube auch, dass diese Flüchtlingsbewegung, die jetzt eingetreten sind, eine Chance ist für Kinder, in der Schule sich schon damit zu beschäftigen.
-Das erlebe ich nämlich, dass schon Schulkinder lernen, wo kommen die anderen her, warum sind die da – das ist auch eine Chance.
-Küpper: Dann noch kurz: Das Gericht hat den Attentäter zu 14 Jahren Freiheitsstrafe verurteilt, allerdings niederer Beweggründe dabei verneint, obwohl es ja klar eine rechtsextreme Gewaltbereitschaft damals gab.
-Das ist ein – kann man, glaube ich, so sagen – recht mildes Urteil gewesen.
-Welche Botschaft geht davon aus?
-Reker: Also, ich konnte das nicht nachvollziehen, dass man die niedrigen Beweggründe nicht angenommen hat.
-Ich muss Ihnen sagen, ich finde das jetzt für mich persönlich nicht wichtig, ob der Attentäter zu 14 oder 15 Jahren verurteilt wird.
-Küpper: Aber wir sprechen über die gesellschaftliche ...
-Reker: Also, ich kann einfach nicht nachvollziehen, wie jemand aus rechter Gewalt töten will und das soll kein niedriger Beweggrund sein.
-Und deswegen habe ich auch so eine Sorge vor der Revision, die ich niemals eingelegt hätte.
-Ich stelle mir mir Grausen vor, dass ein Bundesgericht bestätigt, dass man aus rechter Gewalt einen Mordversuch macht und das keine niedrigen Beweggründe sein sollen.
-Ich bin mal sehr gespannt.
-"""""""""""""""" Es sind viele positive Dinge übrig geblieben von der Silvesternacht"""""""""""""""" Küpper: Sie hören das Interview der Woche im Deutschlandfunk.
-Zu Gast ist Henriette Reker, die Oberbürgermeisterin der Stadt Köln.
-Frau Reker, am Anfang des Jahres, da stand die Silvesternacht – die ist mittlerweile ein geflügeltes Wort, gerade im Kontext von Köln.
-Wie viel von dieser Silvesternacht ist in Ihrer Stadt noch zu spüren?
-Reker: Es ist ganz viel Positives von dieser Silvesternacht zu spüren.
-Küpper: Was?
-Reker: Die Silvesternacht hat mich ja dazu gebracht, ein """""""""""""""" Stärkungsmodell Sicherheit"""""""""""""""" zu konstruieren.
-Eine Zusammenarbeit, eine institutionelle Zusammenarbeit mit der Polizei, die es in dieser Form noch nie gegeben hat in Köln.
-Und es hat auch einen stärkeren Personaleinsatz gegeben für die Polizei, die Stadt hat 100 Ordnungskräfte mehr auf der Straße.
-Es sind viele positive Dinge übrig geblieben von der Silvesternacht.
-Küpper: Das Image hat nicht gelitten?
-Reker: Das Image hat gelitten.
-Aber ich glaube, das Schlimmste daran, an Silvester, war wirklich das Trauma der überfallenen Frauen, dass sicherlich nicht nach wenigen Monaten ausgestanden ist.
-Denen galt auch mein erster Gedanke.
-Aber mitzuweinen hat da wenig Zweck.
-Da geht es darum zu handeln und solche Dinge in der Zukunft zu verhindern.
-Das habe ich getan.
-Küpper: Dennoch muss die Sache auch aufgearbeitet werden, das haben Sie ja auch gerade gesagt.
-Wenn man da auf die juristische Seite guckt, ich habe diese Woche mal beim Amtsgericht nachgefragt, da sind jetzt 15 Urteile gefällt worden.
-Angesichts der Tatsache, der hohen Zahl von Anzeigen – über 1.000 – und Anzahl der jetzt über acht Monate, die verstrichen sind seitdem, wie zufrieden sind Sie mit dem?
-Reker: Gar nicht zufrieden.
-Gar nicht zufrieden.
-Aber das war ja zu erwarten, dass es sehr schwerfallen wird, dass die Frauen dann diese Täter wiedererkennen.
-Also, das geht im Einzelfall, aber ganz überwiegend geht es eben nicht.
-Und das ist daran wirklich schlimm, dass die Männer nicht zur Rechenschaft gezogen werden können.
-Küpper: Das heißt, es war klar, dass diese Erwartungshaltung, die es da ein stückweit gab, automatisch enttäuscht werden musste?
-Reker: Ich habe das befürchtet, ja.
-"""""""""""""""" Es wird hier Wahlkampf mit einem schrecklichen Vorfall in unserer Stadt gemacht"""""""""""""""" Küpper: Wenn wir auf die politische Aufarbeitung gucken, da gibt es im Düsseldorfer Landtag einen parlamentarischen Untersuchungsausschuss, vor dem Sie ja auch schon als Zeugin ausgesagt haben.
-Allerdings gibt es jetzt hier in wenigen Monaten Wahlen in Nordrhein-Westfalen.
-Wie groß ist Ihre Hoffnung, dass aus diesem Ausschuss, aus dieser Ausschussarbeit wirklich etwas Konstruktives für Sie, für die Stadt, für die Opfer herauskommen kann?
-Reker: Also, ich gebe die Hoffnung ja nie auf.
-Aber in dem Ausschuss geht es im Wesentlichen, nach meiner Wahrnehmung, darum, wer schuld ist und nicht darum, weiterzuentwickeln, welche gesellschaftlichen Konsequenzen jetzt aus diesen schrecklichen Vorfällen gezogen werden.
-Küpper: Es geht auch um die Aufarbeitung, aber das scheint ...
-Reker: Es ist ein verschobenes Thema.
-Es wird hier Wahlkampf mit einem schrecklichen Vorfall unserer Stadt gemacht und das kann mir nicht gefallen.
-Küpper: Im Kontext dieser Silvesternacht fiel auch diese, ja, man muss mittlerweile ja fast sagen, berühmte Armlängen-Äußerung, die Sie getätigt haben.
-Was hat Sie diese Diskussion danach darüber – nicht über die Silvesternacht selber, nicht über die Ereignisse, sondern nur um Ihre Äußerung – gelehrt?
-Reker: Dass es einen Grund gibt, warum Politiker vorgefertigte Antworten geben und nicht spontan antworten, so wie ich mir das erhalten will.
-Es hat mich auch gelehrt, nicht darauf zu setzen, dass Zitate wirklich so gebracht werden, wie sie gefallen sind, nämlich als Beispiel.
-Und es hat mich auch nachdenklich gemacht, hinsichtlich der Zielrichtung vieler Journalisten.
-"""""""""""""""" Mit Shitstorms werde ich fertig"""""""""""""""" Küpper: Sie haben mal gesagt: """""""""""""""" Ich war die mit dem Attentat, dann war ich die mit der Armlänge"""""""""""""""" .
-Das heißt, kann man überhaupt in unserem öffentlichen Raum dann noch ordentliche Debatten führen, wenn das nur so auf Schlagworte verkürzt wird?
-Reker: Ja, das kann man.
-Und man muss es sogar.
-Und das können die Bürgerinnen und Bürger auch von uns erwarten.
-Ich bin da nicht bereit, mich zu lange bei Dingen aufzuhalten, die letztlich nicht zu einem Ergebnis oder zu einem Ziel führen.
-Wir haben hier eine Millionenstadt, die will nicht nur verwaltet, sondern gesteuert werden, die soll nach vornegebracht werden, da darf man dann nicht so viel Sorgen und Zeit verschwenden, wenn Shitstorms kommen – damit werde ich fertig.
-"""""""""""""""" Man erwartet von eiener Frau, dass sie Probleme emotionaler begleitet"""""""""""""""" Küpper: Sie hören den Deutschlandfunk, das Interview der Woche, mit Henriette Reker, der Kölner Oberbürgermeisterin.
-Frau Reker, Sie sind jetzt etwa ein Dreivierteljahr im Amt.
-Frau Merkel war die erste Frau im Bundeskanzleramt.
-Hannelore Kraft war die erste Frau in Nordrhein-Westfalen.
-Sie sind die erste Frau an der Spitze einer deutschen Millionenstadt.
-Spielt das überhaupt noch eine Rolle?
-Reker: Vor einem halben Jahr hätte ich noch gesagt: 'Es spielt keine Rolle.
-' Inzwischen glaube ich, dass es doch so ist, dass zu mir noch eine emotionalere Bindung aufgebaut wird von den Kölnerinnen und Kölner als zu einem Mann an der Spitze.
-Küpper: Wie erklären Sie sich das?
-Reker: Ja, vielleicht dadurch, dass ich mich ganz und gar dieser Stadt zuwende und mich auch auf jeden einzelnen Gesprächspartner einstelle, weil es mich wirklich interessiert und weil man von einer Frau eben auch erwartet, dass sie Probleme emotionaler begleitet.
-Wenn Sie sehen, wie oft ich umarmt und geküsst werden, wenn ich durch die Stadt gehe, dann würden Sie sich wundern.
-Küpper: Sie sind nicht nur die erste Frau an der Spitze einer deutschen Millionenstadt, sondern Sie sind auch die erste parteilose Oberbürgermeisterin.
-Was ist so schlecht an Parteien?
-Reker: Es ist gar nichts Schlechtes an Parteien.
-Wir brauchen die Parteien unbedingt.
-Küpper: Aber Sie brauchen keine?
-Reker: Ich brauchte noch nie eine, nein.
-Mir geht es ganz und gar um die Sache, das war immer schon so.
-Mir geht es ganz und gar um Köln.
-Und es gibt keinen roten, grünen oder schwarzen Kreisverkehr, sondern entweder braucht die Stadt einen oder sie braucht ihn nicht.
-"""""""""""""""" Die öffentliche Hand ist ganz überwiegend überfordert mit dem Bau von Großprojekten"""""""""""""""" Küpper: Ein Anliegen oder eine Aufgabe der Kommunen – nicht nur der Kommunen, sondern der öffentlichen Hand – sind ja häufig auch Großprojekte.
-Das funktioniert nicht immer gut in Köln, Stichwort """""""""""""""" Oper"""""""""""""""" .
-Aber Köln ist damit ja auch nicht alleine, also, Berlin, Stuttgart 21, die Elbphilharmonie in Hamburg, man könnte die Liste jetzt wahrscheinlich beliebig fortsetzen.
-Was lehrt einen das?
-Reker: Die öffentliche Hand ist, meines Erachtens, ganz überwiegend überfordert mit dem Bau von Großprojekten.
-Wenn das gelingt, dauert es länger und ist auch kostspieliger.
-Das liegt eben an den Vorschriften, die für die öffentliche Hand bestehen und es liegt daran, dass in den Haushalten – und auch das ist in allen Städten sehr vergleichbar – immer wenig Luft ist.
-Und ein Großprojekt eben dann funktioniert, wenn es am Anfang gründlich geplant wird, wenn man viel Geld für die Planung in die Hand nimmt und auch ehrlich berechnet, was wird es kosten, also auch immer einen Zuschlag von 15 oder 20 Prozent für Unvorhergesehenes einkalkuliert.
-Und wenn man dann ehrlich ist zur Politik, dann wird das eine solche Bausumme, die sich dann keiner mehr traut zu beschließen.
-Deswegen wird meist auf dieses Unvorhergesehene verzichtet.
-Und das möchte ich in Köln schon ehrlicher haben in Zukunft.
-Da soll man wissen, was auf einen zukommt.
-Küpper: Frau Reker, dann zum Abschluss.
-Am Jahreswechsel wird wahrscheinlich noch einmal die ganze Welt nach Köln schauen, das hängt naturgemäß damit zusammen, dass das dieses Jahr jetzt mit der Kölner Silvesternacht gestartet ist.
-Wie kann sich die Stadt darauf vorbereiten?
-Reker: Ja, wir werden natürlich die Erfahrungen, die wir aus dem vorigen Jahr mitgenommen haben, in Konzepte für das nächste Jahr bringen und uns genau überlegen, wie man das machen kann.
-Wir haben seitdem ja auch andere Großveranstaltungen erfolgreich durchgeführt – ich denke nur an Cologne Pride, also Christopher Street Day, ich denke an den Karneval.
-Und – ja – ich werden den Polizeipräsidenten einladen, mit mir Silvester zu feiern, dann sitzen wir schon mal zusammen.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -708,7 +395,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="336" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -727,7 +414,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="266" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +433,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -757,7 +444,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.75" customWidth="1"/>
@@ -765,36 +452,7 @@
     <col min="3" max="3" width="21.5" customWidth="1"/>
     <col min="4" max="4" width="22.1640625" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="409.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/260905.xlsx
+++ b/260905.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F31D471-7A26-4042-BC1F-1E5D14FBA056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB04892-DEF0-4847-9F78-AC60D3B69DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4490" yWindow="2140" windowWidth="15030" windowHeight="11170" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7910" yWindow="2720" windowWidth="15010" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,37 +28,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>dass der Stärkste sich davor drückt, zum Gemeinwohl beizutragen.
-Geers: Das heißt aber auch, aus Ihrer Sicht wackelt dann zum Beispiel das Thema Haushaltsausgleich – dann wackelt die schwarze Null nicht unbedingt?
-wenn man eine zweite Bedingung einhält und gleich klärt, wie man eigentlich das wieder abbezahlt.
-in der wir ausgeglichene Haushalte haben.
-Und das ist der Grund, warum ich als Wirtschaftsminister sage: Das klappt alles nur.
-Und da gibt es eine Reihe von Dingen, wo wir in den letzten Jahren, glaube ich, nicht genug gemacht haben.
-Geers: Als da wären? 
-Gabriel: Zum Beispiel die Entlastung von mittelständischen Unternehmen dort, wo sie.
-Wir haben Regeln,die zum Teil 15,20 Jahre alt sind bei der Frage</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ist die Anzahl der Belegschaft nicht zurückgegangen.
-Es hat sich aber ein Wandel in den Arbeitsplätzen ergeben, wie ich vorhin schon.
-Wir haben ein hohes Maß an Training aufgewandt in den letzten Jahren.
-Also, wir sehen keinen Schwund an Arbeitsplätzen, aber eine andere Qualität an Arbeitsplätzen.
-Hahne: als im letzten Jahr viele Flüchtlinge nach Deutschland gekommen sind, war die Wirtschaft zunächst relativ euphorisch.
-Die Hoffnung, die mitschwang, war.
-Ford hat ein Praktikantenprogramm ?
-Mattes: in mehrerlei Hinsicht.
-Erstens einmal</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Lässt sich daran vielleicht ein Stück weit auch das aktuelle Verhältnis der deutschen Gesellschaft hinsichtlich der DITIB ablesen?
 Reker: Ich glaube nicht.
 Ich finde den Moscheebau wunderbar, auch an der Stelle.
 zur Beseitigung eingeklagt wurden.
 ganz glasklar die Auffassung vertreten, dass es eine städtische Förderung nur geben kann, wenn wie jede andere Kirchengemeinde auch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wackelt Haushaltsausgleich</t>
+  </si>
+  <si>
+    <t>einhält</t>
+  </si>
+  <si>
+    <t>abbezahlt</t>
+  </si>
+  <si>
+    <t>alt sind</t>
+  </si>
+  <si>
+    <t>Belegschaft</t>
+  </si>
+  <si>
+    <t>wie ich vorhin schon. hohes Maß an Training aufgewandt</t>
+  </si>
+  <si>
+    <t>mehrerlei Hinsicht</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hoffnung, die mitschwang, war  同...一起振动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Schwund 缩减</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -387,15 +393,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76C6683F-548D-4BAD-95B9-AE790692AEB2}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="336" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -406,15 +427,35 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAC7E1F0-F588-442A-9AC0-291DE8687BF4}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="266" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -433,7 +474,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="238" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/260905.xlsx
+++ b/260905.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB04892-DEF0-4847-9F78-AC60D3B69DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E172CF-7DE2-4C5B-B5C8-2E91691055E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7910" yWindow="2720" windowWidth="15010" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9960" yWindow="3700" windowWidth="15010" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>Belegschaft</t>
   </si>
   <si>
-    <t>wie ich vorhin schon. hohes Maß an Training aufgewandt</t>
-  </si>
-  <si>
     <t>mehrerlei Hinsicht</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -65,6 +62,10 @@
   </si>
   <si>
     <t>Schwund 缩减</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wie ich vorhin schon. hohes Maß an Training aufgewandt(aufwenden 花费)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -440,22 +441,22 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
